--- a/xunfang/templates/jiemiansanleijingqing_template.xlsx
+++ b/xunfang/templates/jiemiansanleijingqing_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12200" activeTab="3"/>
+    <workbookView windowWidth="25600" windowHeight="12200" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="人身伤害类" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="28">
   <si>
     <t>2026年</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>确认警情环比幅度</t>
-  </si>
-  <si>
-    <t>12月27日—1月2日</t>
   </si>
   <si>
     <t>云城</t>
@@ -1558,11 +1555,9 @@
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:30">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1644,7 +1639,7 @@
     <row r="7" ht="16.5" spans="1:30">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -1726,7 +1721,7 @@
     <row r="8" ht="16.5" spans="1:30">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -1808,7 +1803,7 @@
     <row r="9" ht="16.5" spans="1:30">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -1890,7 +1885,7 @@
     <row r="10" ht="16.5" spans="1:30">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -1971,7 +1966,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:30">
       <c r="A11" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
@@ -2156,7 +2151,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2323,11 +2318,9 @@
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:30">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -2409,7 +2402,7 @@
     <row r="7" ht="16.5" spans="1:30">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -2491,7 +2484,7 @@
     <row r="8" ht="16.5" spans="1:30">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -2573,7 +2566,7 @@
     <row r="9" ht="16.5" spans="1:30">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -2655,7 +2648,7 @@
     <row r="10" ht="16.5" spans="1:30">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -2736,7 +2729,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:30">
       <c r="A11" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
@@ -2921,7 +2914,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -3088,11 +3081,9 @@
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:30">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -3174,7 +3165,7 @@
     <row r="7" ht="16.5" spans="1:30">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -3256,7 +3247,7 @@
     <row r="8" ht="16.5" spans="1:30">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -3338,7 +3329,7 @@
     <row r="9" ht="16.5" spans="1:30">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -3420,7 +3411,7 @@
     <row r="10" ht="16.5" spans="1:30">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -3501,7 +3492,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:30">
       <c r="A11" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
@@ -3618,7 +3609,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -3785,11 +3776,9 @@
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:30">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -3871,7 +3860,7 @@
     <row r="7" ht="16.5" spans="1:30">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -3953,7 +3942,7 @@
     <row r="8" ht="16.5" spans="1:30">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -4035,7 +4024,7 @@
     <row r="9" ht="16.5" spans="1:30">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -4117,7 +4106,7 @@
     <row r="10" ht="16.5" spans="1:30">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -4198,7 +4187,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:30">
       <c r="A11" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="14"/>

--- a/xunfang/templates/jiemiansanleijingqing_template.xlsx
+++ b/xunfang/templates/jiemiansanleijingqing_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12200" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="12200" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="人身伤害类" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="29">
   <si>
     <t>2026年</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>确认警情环比幅度</t>
+  </si>
+  <si>
+    <t>12月27日—1月2日</t>
   </si>
   <si>
     <t>云城</t>
@@ -1555,9 +1558,11 @@
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:30">
-      <c r="A6" s="13"/>
+      <c r="A6" s="13" t="s">
+        <v>19</v>
+      </c>
       <c r="B6" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1639,7 +1644,7 @@
     <row r="7" ht="16.5" spans="1:30">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -1721,7 +1726,7 @@
     <row r="8" ht="16.5" spans="1:30">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -1803,7 +1808,7 @@
     <row r="9" ht="16.5" spans="1:30">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -1885,7 +1890,7 @@
     <row r="10" ht="16.5" spans="1:30">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -1966,7 +1971,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:30">
       <c r="A11" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
@@ -2151,7 +2156,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2318,9 +2323,11 @@
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:30">
-      <c r="A6" s="13"/>
+      <c r="A6" s="13" t="s">
+        <v>19</v>
+      </c>
       <c r="B6" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -2402,7 +2409,7 @@
     <row r="7" ht="16.5" spans="1:30">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -2484,7 +2491,7 @@
     <row r="8" ht="16.5" spans="1:30">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -2566,7 +2573,7 @@
     <row r="9" ht="16.5" spans="1:30">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -2648,7 +2655,7 @@
     <row r="10" ht="16.5" spans="1:30">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -2729,7 +2736,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:30">
       <c r="A11" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
@@ -2914,7 +2921,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -3081,9 +3088,11 @@
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:30">
-      <c r="A6" s="13"/>
+      <c r="A6" s="13" t="s">
+        <v>19</v>
+      </c>
       <c r="B6" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -3165,7 +3174,7 @@
     <row r="7" ht="16.5" spans="1:30">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -3247,7 +3256,7 @@
     <row r="8" ht="16.5" spans="1:30">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -3329,7 +3338,7 @@
     <row r="9" ht="16.5" spans="1:30">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -3411,7 +3420,7 @@
     <row r="10" ht="16.5" spans="1:30">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -3492,7 +3501,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:30">
       <c r="A11" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
@@ -3609,7 +3618,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -3776,9 +3785,11 @@
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:30">
-      <c r="A6" s="13"/>
+      <c r="A6" s="13" t="s">
+        <v>19</v>
+      </c>
       <c r="B6" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -3860,7 +3871,7 @@
     <row r="7" ht="16.5" spans="1:30">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -3942,7 +3953,7 @@
     <row r="8" ht="16.5" spans="1:30">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -4024,7 +4035,7 @@
     <row r="9" ht="16.5" spans="1:30">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -4106,7 +4117,7 @@
     <row r="10" ht="16.5" spans="1:30">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -4187,7 +4198,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:30">
       <c r="A11" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="14"/>
